--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -56,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>客户名称</t>
     </r>
     <r>
@@ -71,6 +78,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>所属分类</t>
     </r>
     <r>
@@ -92,6 +106,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>联系人</t>
     </r>
     <r>
@@ -109,8 +130,33 @@
     <t>负责人</t>
   </si>
   <si>
-    <r>
-      <t>地区</t>
+    <t>地区</t>
+  </si>
+  <si>
+    <t>国家</t>
+  </si>
+  <si>
+    <t>省</t>
+  </si>
+  <si>
+    <t>市</t>
+  </si>
+  <si>
+    <t>区</t>
+  </si>
+  <si>
+    <t>地址</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电话</t>
     </r>
     <r>
       <rPr>
@@ -125,7 +171,14 @@
   </si>
   <si>
     <r>
-      <t>国家</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手机</t>
     </r>
     <r>
       <rPr>
@@ -139,8 +192,30 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>省</t>
+    <t>传真</t>
+  </si>
+  <si>
+    <t>邮政编码</t>
+  </si>
+  <si>
+    <t>邮箱</t>
+  </si>
+  <si>
+    <t>网址</t>
+  </si>
+  <si>
+    <t>渠道类型</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>付款方式</t>
     </r>
     <r>
       <rPr>
@@ -155,7 +230,14 @@
   </si>
   <si>
     <r>
-      <t>市</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>付款周期</t>
     </r>
     <r>
       <rPr>
@@ -170,7 +252,14 @@
   </si>
   <si>
     <r>
-      <t>区</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对账开始日期</t>
     </r>
     <r>
       <rPr>
@@ -185,7 +274,14 @@
   </si>
   <si>
     <r>
-      <t>地址</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对账结束日期</t>
     </r>
     <r>
       <rPr>
@@ -207,7 +303,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>电话</t>
+      <t>税率</t>
     </r>
     <r>
       <rPr>
@@ -221,111 +317,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <t>传真</t>
-  </si>
-  <si>
-    <t>邮政编码</t>
-  </si>
-  <si>
-    <t>邮箱</t>
-  </si>
-  <si>
-    <t>网址</t>
-  </si>
-  <si>
-    <t>渠道类型</t>
-  </si>
-  <si>
-    <r>
-      <t>付款方式</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>付款周期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>对账开始日期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>对账结束日期</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>税率</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -359,7 +350,7 @@
     <t>付款周期一般为：30天、45天、60天、70天、90天，详见新建客户维护的付款周期下拉项</t>
   </si>
   <si>
-    <t>对账开始日期和对账结束日期输入格式为：2024-06-11</t>
+    <t>对账开始日期和对账结束日期输入格式为：06-11</t>
   </si>
 </sst>
 </file>
@@ -1624,29 +1615,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.775" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
+    <col min="9" max="9" width="15.225" customWidth="1"/>
     <col min="10" max="10" width="15.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.1111111111111" customWidth="1"/>
-    <col min="12" max="12" width="11.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="14.1083333333333" customWidth="1"/>
+    <col min="12" max="12" width="11.5583333333333" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="16.775" customWidth="1"/>
     <col min="15" max="21" width="14.6666666666667" customWidth="1"/>
     <col min="22" max="22" width="18.3333333333333" customWidth="1"/>
     <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="22.4444444444444" customWidth="1"/>
+    <col min="24" max="24" width="22.4416666666667" customWidth="1"/>
     <col min="25" max="25" width="20.3333333333333" customWidth="1"/>
     <col min="26" max="26" width="14.6666666666667" customWidth="1"/>
-    <col min="27" max="27" width="19.4444444444444" customWidth="1"/>
+    <col min="27" max="27" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:27">
@@ -1819,9 +1810,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
@@ -1854,7 +1845,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" ht="31.2" spans="1:1">
+    <row r="7" ht="28.5" spans="1:1">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>序号</t>
   </si>
@@ -130,6 +130,24 @@
     <t>负责人</t>
   </si>
   <si>
+    <t>所属销售</t>
+  </si>
+  <si>
+    <t>所属部门</t>
+  </si>
+  <si>
+    <t>内勤人员</t>
+  </si>
+  <si>
+    <t>下次联系时间</t>
+  </si>
+  <si>
+    <t>认定日期</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
     <t>地区</t>
   </si>
   <si>
@@ -207,6 +225,15 @@
     <t>渠道类型</t>
   </si>
   <si>
+    <t>运输方式</t>
+  </si>
+  <si>
+    <t>运输时间（天）</t>
+  </si>
+  <si>
+    <t>行业类别</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -295,6 +322,9 @@
     </r>
   </si>
   <si>
+    <t>开票类型</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -317,40 +347,118 @@
     </r>
   </si>
   <si>
+    <t>开户银行</t>
+  </si>
+  <si>
+    <t>银行账号</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>产品编码：需根据编码规则设置中，如果是自动生成，则无需填写，如果是手动输入，则必须输入</t>
-  </si>
-  <si>
-    <t>客户编码唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
-  </si>
-  <si>
-    <t>电话和手机二选一，必填一项</t>
-  </si>
-  <si>
-    <t>所属分类填写客户分类名称</t>
-  </si>
-  <si>
-    <t>地区填写国内或国外</t>
-  </si>
-  <si>
-    <t>国家全部填写简称，如：中华人民共和国，填写中国</t>
-  </si>
-  <si>
-    <t>省、市、区全部填写全称，如浙江省，就填浙江省，不要填浙江。如国外地区时，省、市、区都不用填写，直接写地址即可。</t>
-  </si>
-  <si>
-    <t>付款方式填写新增页面上的下拉项，一般为：银行转账、银行承兑汇票</t>
-  </si>
-  <si>
-    <t>付款周期一般为：30天、45天、60天、70天、90天，详见新建客户维护的付款周期下拉项</t>
-  </si>
-  <si>
-    <t>对账开始日期和对账结束日期输入格式为：06-11</t>
+    <t>国内</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>浙江省</t>
+  </si>
+  <si>
+    <t>宁波市</t>
+  </si>
+  <si>
+    <t>鄞州区</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>快递</t>
+  </si>
+  <si>
+    <t>五金/工具</t>
+  </si>
+  <si>
+    <t>现金</t>
+  </si>
+  <si>
+    <t>30天</t>
+  </si>
+  <si>
+    <t>11-20</t>
+  </si>
+  <si>
+    <t>11-25</t>
+  </si>
+  <si>
+    <t>增值税专用发票</t>
+  </si>
+  <si>
+    <t>13%</t>
+  </si>
+  <si>
+    <t>客户编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
+  </si>
+  <si>
+    <t>电话和手机：二选一，必填一项</t>
+  </si>
+  <si>
+    <t>所属分类：填写客户分类名称</t>
+  </si>
+  <si>
+    <t>所属销售、内勤人员：填入人员名称</t>
+  </si>
+  <si>
+    <t>所属部门：填入部门名称</t>
+  </si>
+  <si>
+    <t>下次联系时间：输入格式，如：yyyy-MM-dd</t>
+  </si>
+  <si>
+    <t>认定日期：输入格式，如：yyyy-MM-dd</t>
+  </si>
+  <si>
+    <t>等级：对应页面上的等级</t>
+  </si>
+  <si>
+    <t>地区：填写国内或国外</t>
+  </si>
+  <si>
+    <t>国家：全部填写简称，如：中华人民共和国，填写中国</t>
+  </si>
+  <si>
+    <t>省、市、区：全部填写全称，如浙江省，就填浙江省，不要填浙江。如国外地区时，省、市、区都不用填写，直接写地址即可。</t>
+  </si>
+  <si>
+    <t>渠道类型：对应页面下拉的渠道类型</t>
+  </si>
+  <si>
+    <t>运输方式：对应页面下拉的运输方式</t>
+  </si>
+  <si>
+    <t>运输时间（天 ）：输入整数</t>
+  </si>
+  <si>
+    <t>行业类别：对应页面下拉的行业类别</t>
+  </si>
+  <si>
+    <t>付款方式：填写新增页面上的下拉项，一般为：银行转账、银行承兑汇票</t>
+  </si>
+  <si>
+    <t>付款周期：一般为：30天、45天、60天、70天、90天，详见新建客户维护的付款周期下拉项</t>
+  </si>
+  <si>
+    <t>对账开始日期和对账结束日期：输入格式为：06-11</t>
+  </si>
+  <si>
+    <t>开票类型：对应页面下拉的开票类型</t>
+  </si>
+  <si>
+    <t>税率：对应页面下拉税率，如：13%</t>
   </si>
 </sst>
 </file>
@@ -1614,33 +1722,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AM48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.225" customWidth="1"/>
-    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.775" customWidth="1"/>
-    <col min="8" max="8" width="10.225" customWidth="1"/>
-    <col min="9" max="9" width="15.225" customWidth="1"/>
-    <col min="10" max="10" width="15.3333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.1083333333333" customWidth="1"/>
-    <col min="12" max="12" width="11.5583333333333" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16.775" customWidth="1"/>
-    <col min="15" max="21" width="14.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="18.3333333333333" customWidth="1"/>
-    <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="22.4416666666667" customWidth="1"/>
-    <col min="25" max="25" width="20.3333333333333" customWidth="1"/>
-    <col min="26" max="26" width="14.6666666666667" customWidth="1"/>
-    <col min="27" max="27" width="19.4416666666667" customWidth="1"/>
+    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
+    <col min="9" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="17.1111111111111" customWidth="1"/>
+    <col min="13" max="14" width="14.1111111111111" customWidth="1"/>
+    <col min="15" max="15" width="15.2222222222222" customWidth="1"/>
+    <col min="16" max="16" width="15.3333333333333" customWidth="1"/>
+    <col min="17" max="17" width="14.1111111111111" customWidth="1"/>
+    <col min="18" max="18" width="11.5555555555556" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="16.7777777777778" customWidth="1"/>
+    <col min="21" max="28" width="14.6666666666667" customWidth="1"/>
+    <col min="29" max="30" width="15.8888888888889" customWidth="1"/>
+    <col min="31" max="31" width="18.3333333333333" customWidth="1"/>
+    <col min="32" max="32" width="17" customWidth="1"/>
+    <col min="33" max="33" width="22.4444444444444" customWidth="1"/>
+    <col min="34" max="35" width="20.3333333333333" customWidth="1"/>
+    <col min="36" max="38" width="14.6666666666667" customWidth="1"/>
+    <col min="39" max="39" width="19.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:27">
+    <row r="1" ht="25" customHeight="1" spans="1:39">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1719,13 +1831,49 @@
       <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:27">
+    <row r="2" ht="20" customHeight="1" spans="1:39">
       <c r="A2" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1740,11 +1888,21 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
+      <c r="O2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
@@ -1752,7 +1910,37 @@
       <c r="X2" s="8"/>
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
-      <c r="AA2" s="5"/>
+      <c r="AA2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK2" s="8"/>
+      <c r="AL2" s="8"/>
+      <c r="AM2" s="5"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1809,77 +1997,125 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
+  <dimension ref="A1:A33"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:1">
+    <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1"/>
-    <row r="12" ht="28" customHeight="1"/>
-    <row r="13" ht="28" customHeight="1"/>
-    <row r="14" ht="28" customHeight="1"/>
-    <row r="15" ht="28" customHeight="1"/>
-    <row r="16" ht="28" customHeight="1"/>
-    <row r="17" ht="28" customHeight="1"/>
-    <row r="18" ht="28" customHeight="1"/>
-    <row r="19" ht="28" customHeight="1"/>
-    <row r="20" ht="28" customHeight="1"/>
+    <row r="11" ht="28" customHeight="1" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="21" ht="28" customHeight="1"/>
     <row r="22" ht="28" customHeight="1"/>
     <row r="23" ht="28" customHeight="1"/>
     <row r="24" ht="28" customHeight="1"/>
     <row r="25" ht="28" customHeight="1"/>
+    <row r="26" ht="28" customHeight="1"/>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="28" customHeight="1"/>
+    <row r="29" ht="28" customHeight="1"/>
+    <row r="30" ht="28" customHeight="1"/>
+    <row r="31" ht="28" customHeight="1"/>
+    <row r="32" ht="28" customHeight="1"/>
+    <row r="33" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
@@ -228,7 +228,7 @@
     <t>运输方式</t>
   </si>
   <si>
-    <t>运输时间（天）</t>
+    <t>运输时间(天)</t>
   </si>
   <si>
     <t>行业类别</t>
@@ -1723,33 +1723,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AM48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.775" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
     <col min="9" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="17.1111111111111" customWidth="1"/>
-    <col min="13" max="14" width="14.1111111111111" customWidth="1"/>
-    <col min="15" max="15" width="15.2222222222222" customWidth="1"/>
+    <col min="12" max="12" width="17.1083333333333" customWidth="1"/>
+    <col min="13" max="14" width="14.1083333333333" customWidth="1"/>
+    <col min="15" max="15" width="15.225" customWidth="1"/>
     <col min="16" max="16" width="15.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="14.1111111111111" customWidth="1"/>
-    <col min="18" max="18" width="11.5555555555556" customWidth="1"/>
+    <col min="17" max="17" width="14.1083333333333" customWidth="1"/>
+    <col min="18" max="18" width="11.5583333333333" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="16.7777777777778" customWidth="1"/>
+    <col min="20" max="20" width="16.775" customWidth="1"/>
     <col min="21" max="28" width="14.6666666666667" customWidth="1"/>
-    <col min="29" max="30" width="15.8888888888889" customWidth="1"/>
+    <col min="29" max="30" width="15.8916666666667" customWidth="1"/>
     <col min="31" max="31" width="18.3333333333333" customWidth="1"/>
     <col min="32" max="32" width="17" customWidth="1"/>
-    <col min="33" max="33" width="22.4444444444444" customWidth="1"/>
+    <col min="33" max="33" width="22.4416666666667" customWidth="1"/>
     <col min="34" max="35" width="20.3333333333333" customWidth="1"/>
     <col min="36" max="38" width="14.6666666666667" customWidth="1"/>
-    <col min="39" max="39" width="19.4444444444444" customWidth="1"/>
+    <col min="39" max="39" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:39">
@@ -1998,9 +1998,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A33"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
@@ -105,26 +105,7 @@
     <t>英文名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>联系人</t>
   </si>
   <si>
     <t>负责人</t>
@@ -166,48 +147,10 @@
     <t>地址</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电话</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>手机</t>
   </si>
   <si>
     <t>传真</t>
@@ -404,7 +347,7 @@
     <t>客户编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
   </si>
   <si>
-    <t>电话和手机：二选一，必填一项</t>
+    <t>电话和手机：非必填</t>
   </si>
   <si>
     <t>所属分类：填写客户分类名称</t>
@@ -1723,33 +1666,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AM48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="13.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="10.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
+    <col min="6" max="6" width="13.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.775" customWidth="1"/>
+    <col min="8" max="8" width="10.225" customWidth="1"/>
     <col min="9" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="17.1111111111111" customWidth="1"/>
-    <col min="13" max="14" width="14.1111111111111" customWidth="1"/>
-    <col min="15" max="15" width="15.2222222222222" customWidth="1"/>
+    <col min="12" max="12" width="17.1083333333333" customWidth="1"/>
+    <col min="13" max="14" width="14.1083333333333" customWidth="1"/>
+    <col min="15" max="15" width="15.225" customWidth="1"/>
     <col min="16" max="16" width="15.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="14.1111111111111" customWidth="1"/>
-    <col min="18" max="18" width="11.5555555555556" customWidth="1"/>
+    <col min="17" max="17" width="14.1083333333333" customWidth="1"/>
+    <col min="18" max="18" width="11.5583333333333" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="16.7777777777778" customWidth="1"/>
+    <col min="20" max="20" width="16.775" customWidth="1"/>
     <col min="21" max="28" width="14.6666666666667" customWidth="1"/>
-    <col min="29" max="30" width="15.8888888888889" customWidth="1"/>
+    <col min="29" max="30" width="15.8916666666667" customWidth="1"/>
     <col min="31" max="31" width="18.3333333333333" customWidth="1"/>
     <col min="32" max="32" width="17" customWidth="1"/>
-    <col min="33" max="33" width="22.4444444444444" customWidth="1"/>
+    <col min="33" max="33" width="22.4416666666667" customWidth="1"/>
     <col min="34" max="35" width="20.3333333333333" customWidth="1"/>
     <col min="36" max="38" width="14.6666666666667" customWidth="1"/>
-    <col min="39" max="39" width="19.4444444444444" customWidth="1"/>
+    <col min="39" max="39" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:39">
@@ -1998,9 +1941,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A33"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -105,26 +105,7 @@
     <t>英文名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>联系人</t>
   </si>
   <si>
     <t>负责人</t>
@@ -166,48 +147,10 @@
     <t>地址</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电话</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>手机</t>
   </si>
   <si>
     <t>传真</t>
@@ -228,7 +171,7 @@
     <t>运输方式</t>
   </si>
   <si>
-    <t>运输时间(天)</t>
+    <t>运输时间（天）</t>
   </si>
   <si>
     <t>行业类别</t>
@@ -404,7 +347,7 @@
     <t>客户编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
   </si>
   <si>
-    <t>电话和手机：二选一，必填一项</t>
+    <t>电话和手机：非必填</t>
   </si>
   <si>
     <t>所属分类：填写客户分类名称</t>

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="27480" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
+    <sheet name="成交客户导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>序号</t>
   </si>
@@ -105,26 +105,7 @@
     <t>英文名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>联系人</t>
   </si>
   <si>
     <t>负责人</t>
@@ -166,48 +147,10 @@
     <t>地址</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>电话</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>手机</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>手机</t>
   </si>
   <si>
     <t>传真</t>
@@ -228,7 +171,7 @@
     <t>运输方式</t>
   </si>
   <si>
-    <t>运输时间(天)</t>
+    <t>运输时间（天）</t>
   </si>
   <si>
     <t>行业类别</t>
@@ -359,21 +302,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>国内</t>
-  </si>
-  <si>
-    <t>中国</t>
-  </si>
-  <si>
-    <t>浙江省</t>
-  </si>
-  <si>
-    <t>宁波市</t>
-  </si>
-  <si>
-    <t>鄞州区</t>
-  </si>
-  <si>
     <t>其他</t>
   </si>
   <si>
@@ -404,7 +332,7 @@
     <t>客户编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
   </si>
   <si>
-    <t>电话和手机：二选一，必填一项</t>
+    <t>电话和手机：非必填</t>
   </si>
   <si>
     <t>所属分类：填写客户分类名称</t>
@@ -1888,21 +1816,11 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
@@ -1911,32 +1829,32 @@
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
       <c r="AA2" s="8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AC2" s="8"/>
       <c r="AD2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH2" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI2" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ2" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="AK2" s="8"/>
       <c r="AL2" s="8"/>
@@ -2005,102 +1923,102 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1"/>

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="27480" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="客户导入模板" sheetId="1" r:id="rId1"/>
+    <sheet name="成交客户导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>序号</t>
   </si>
@@ -300,21 +300,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>国内</t>
-  </si>
-  <si>
-    <t>中国</t>
-  </si>
-  <si>
-    <t>浙江省</t>
-  </si>
-  <si>
-    <t>宁波市</t>
-  </si>
-  <si>
-    <t>鄞州区</t>
   </si>
   <si>
     <t>其他</t>
@@ -1831,21 +1816,11 @@
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
-      <c r="O2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
@@ -1854,32 +1829,32 @@
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
       <c r="AA2" s="8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AC2" s="8"/>
       <c r="AD2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH2" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI2" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ2" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="AK2" s="8"/>
       <c r="AL2" s="8"/>
@@ -1948,102 +1923,102 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1"/>

--- a/public/static/客户导入模板.xlsx
+++ b/public/static/客户导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27480" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12525"/>
   </bookViews>
   <sheets>
     <sheet name="成交客户导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>序号</t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>13%</t>
-  </si>
-  <si>
-    <t>客户编码：唯一，如果配置是自动生成，则不需经输入，如果是手动输入，则必填</t>
   </si>
   <si>
     <t>电话和手机：非必填</t>
@@ -1915,7 +1912,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
@@ -2016,11 +2013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
+    <row r="20" ht="28" customHeight="1"/>
     <row r="21" ht="28" customHeight="1"/>
     <row r="22" ht="28" customHeight="1"/>
     <row r="23" ht="28" customHeight="1"/>
@@ -2033,7 +2026,6 @@
     <row r="30" ht="28" customHeight="1"/>
     <row r="31" ht="28" customHeight="1"/>
     <row r="32" ht="28" customHeight="1"/>
-    <row r="33" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
